--- a/shucle_report/영덕관광/20260330_20260405/report_영덕관광_20260330_20260405.xlsx
+++ b/shucle_report/영덕관광/20260330_20260405/report_영덕관광_20260330_20260405.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.30 ~ 04.05 | 비교기간: 2026.03.23 ~ 03.29 | 생성: 2026-04-08 15:25 | 차트: 97개</t>
+          <t>분석기간: 2026.03.30 ~ 04.05 | 비교기간: 2026.03.23 ~ 03.29 | 생성: 2026-04-13 12:24 | 차트: 184개</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.3건</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.0건</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.7명</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -1825,32 +1825,32 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>피크 시간대 이동시간</t>
+          <t>피크 시간대(17~19시) 이동시간</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.9</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+30.5%</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>9.5→12.4분 증가</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>비피크 시간대 이동시간</t>
+          <t>비피크 시간대(11~13시) 이동시간</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2920,6 +2920,13 @@
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>• 이동시간 증가: 4.5분 → 18.0분 (+304%) — 우회비율은 소폭 증가, 경로 효율성 저하</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>• 호출당 평균 탑승객 1.2명: 1인 이용 위주</t>
         </is>
       </c>
     </row>
